--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nlion\OneDrive\문서\GitHub\lotto-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4F49E2-11D7-46B7-B546-3A59596452AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED730BDB-B255-4834-A907-A0B2E13A6CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4309,7 +4309,7 @@
         <v>28</v>
       </c>
       <c r="I2" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>

--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nlion\OneDrive\문서\GitHub\lotto-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED730BDB-B255-4834-A907-A0B2E13A6CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3FB2BA-91BA-4AF2-98C3-AA48700882C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4309,7 +4309,7 @@
         <v>28</v>
       </c>
       <c r="I2" s="6">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>8</v>

--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nlion\OneDrive\문서\GitHub\lotto-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C0A4B6-E990-4CC4-8F44-F5F034922F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1EA2CB-3920-4159-82A3-001610C6EF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="1258">
   <si>
     <t>No</t>
   </si>
@@ -3795,11 +3795,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 원</t>
+    <t>2,698,334,421 원</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4331,10 +4327,10 @@
         <v>8</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>1255</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>1257</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">

--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -3950,6 +3950,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/로또 회차별 당첨번호.xlsx
+++ b/로또 회차별 당첨번호.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62233f832ac04d46/문서/GitHub/lotto-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{AD30BEC9-82BB-4904-8971-56CF2925D13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E55BF75-B8A6-4EE2-9BA6-6B49FC1D70AC}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{AD30BEC9-82BB-4904-8971-56CF2925D13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42DEAB2B-7291-4BC7-84C8-E86E05D9D661}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
